--- a/experiments/depreciatives-experiment.xlsx
+++ b/experiments/depreciatives-experiment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magda\moje\hybrid-agreement\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4BEE3B-75E0-4591-9540-9FC9F2848646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0092F363-7C95-48B1-ACB5-C4271EF9A7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -595,12 +595,6 @@
     <t>Rzeźniki, którzy mają zakład obok, stoją teraz na ulicy.</t>
   </si>
   <si>
-    <t>Na nagraniach do Ameryki Południowej poleciały reżysery.</t>
-  </si>
-  <si>
-    <t>Na nagraniach do Ameryki Południowej polecieli reżysery.</t>
-  </si>
-  <si>
     <t>Reżysery poleciały na nagrania do Ameryki Południowej.</t>
   </si>
   <si>
@@ -908,6 +902,12 @@
   </si>
   <si>
     <t>Czy w zdaniu była mowa o przeprowadzce?</t>
+  </si>
+  <si>
+    <t>Na nagrania do Ameryki Południowej poleciały reżysery.</t>
+  </si>
+  <si>
+    <t>Na nagrania do Ameryki Południowej polecieli reżysery.</t>
   </si>
 </sst>
 </file>
@@ -943,9 +943,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -1263,7 +1262,7 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -1280,7 +1279,7 @@
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -1297,7 +1296,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1314,7 +1313,7 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
@@ -1331,7 +1330,7 @@
         <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
@@ -1348,7 +1347,7 @@
         <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
@@ -1365,10 +1364,10 @@
         <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1382,10 +1381,10 @@
         <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1399,10 +1398,10 @@
         <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1416,10 +1415,10 @@
         <v>136</v>
       </c>
       <c r="D11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1433,10 +1432,10 @@
         <v>137</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1450,10 +1449,10 @@
         <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1467,7 +1466,7 @@
         <v>139</v>
       </c>
       <c r="D14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
@@ -1484,7 +1483,7 @@
         <v>140</v>
       </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
@@ -1501,7 +1500,7 @@
         <v>141</v>
       </c>
       <c r="D16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
@@ -1518,7 +1517,7 @@
         <v>142</v>
       </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
@@ -1535,7 +1534,7 @@
         <v>143</v>
       </c>
       <c r="D18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
@@ -1552,14 +1551,14 @@
         <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>35</v>
       </c>
       <c r="B20" t="s">
@@ -1569,14 +1568,14 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
       <c r="B21" t="s">
@@ -1586,14 +1585,14 @@
         <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>35</v>
       </c>
       <c r="B22" t="s">
@@ -1603,14 +1602,14 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" t="s">
@@ -1620,14 +1619,14 @@
         <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24" t="s">
@@ -1637,14 +1636,14 @@
         <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" t="s">
@@ -1654,14 +1653,14 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>34</v>
       </c>
       <c r="B26" t="s">
@@ -1671,14 +1670,14 @@
         <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
@@ -1688,14 +1687,14 @@
         <v>150</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E27" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>34</v>
       </c>
       <c r="B28" t="s">
@@ -1705,14 +1704,14 @@
         <v>147</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E28" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
@@ -1722,14 +1721,14 @@
         <v>148</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" t="s">
@@ -1739,14 +1738,14 @@
         <v>151</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
@@ -1756,10 +1755,10 @@
         <v>152</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1773,7 +1772,7 @@
         <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
         <v>16</v>
@@ -1790,7 +1789,7 @@
         <v>154</v>
       </c>
       <c r="D33" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E33" t="s">
         <v>16</v>
@@ -1807,7 +1806,7 @@
         <v>155</v>
       </c>
       <c r="D34" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E34" t="s">
         <v>16</v>
@@ -1824,7 +1823,7 @@
         <v>156</v>
       </c>
       <c r="D35" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E35" t="s">
         <v>16</v>
@@ -1841,7 +1840,7 @@
         <v>157</v>
       </c>
       <c r="D36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E36" t="s">
         <v>16</v>
@@ -1858,7 +1857,7 @@
         <v>158</v>
       </c>
       <c r="D37" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
@@ -1875,10 +1874,10 @@
         <v>57</v>
       </c>
       <c r="D38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1892,10 +1891,10 @@
         <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1909,10 +1908,10 @@
         <v>59</v>
       </c>
       <c r="D40" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E40" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1926,10 +1925,10 @@
         <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E41" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1943,10 +1942,10 @@
         <v>61</v>
       </c>
       <c r="D42" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E42" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1960,10 +1959,10 @@
         <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E43" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1977,10 +1976,10 @@
         <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E44" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1994,10 +1993,10 @@
         <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2011,10 +2010,10 @@
         <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E46" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2028,10 +2027,10 @@
         <v>162</v>
       </c>
       <c r="D47" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E47" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2045,10 +2044,10 @@
         <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E48" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2062,10 +2061,10 @@
         <v>164</v>
       </c>
       <c r="D49" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E49" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -2079,7 +2078,7 @@
         <v>165</v>
       </c>
       <c r="D50" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E50" t="s">
         <v>16</v>
@@ -2096,7 +2095,7 @@
         <v>166</v>
       </c>
       <c r="D51" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E51" t="s">
         <v>16</v>
@@ -2113,7 +2112,7 @@
         <v>167</v>
       </c>
       <c r="D52" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
@@ -2130,7 +2129,7 @@
         <v>168</v>
       </c>
       <c r="D53" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
@@ -2147,7 +2146,7 @@
         <v>169</v>
       </c>
       <c r="D54" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E54" t="s">
         <v>16</v>
@@ -2164,7 +2163,7 @@
         <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
@@ -2181,10 +2180,10 @@
         <v>171</v>
       </c>
       <c r="D56" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2198,10 +2197,10 @@
         <v>172</v>
       </c>
       <c r="D57" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E57" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -2215,10 +2214,10 @@
         <v>173</v>
       </c>
       <c r="D58" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E58" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -2232,10 +2231,10 @@
         <v>174</v>
       </c>
       <c r="D59" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E59" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -2249,10 +2248,10 @@
         <v>175</v>
       </c>
       <c r="D60" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E60" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -2266,10 +2265,10 @@
         <v>176</v>
       </c>
       <c r="D61" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E61" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -2283,10 +2282,10 @@
         <v>63</v>
       </c>
       <c r="D62" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E62" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2300,10 +2299,10 @@
         <v>64</v>
       </c>
       <c r="D63" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E63" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2317,10 +2316,10 @@
         <v>65</v>
       </c>
       <c r="D64" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2334,10 +2333,10 @@
         <v>66</v>
       </c>
       <c r="D65" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E65" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -2351,10 +2350,10 @@
         <v>67</v>
       </c>
       <c r="D66" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E66" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2368,10 +2367,10 @@
         <v>68</v>
       </c>
       <c r="D67" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E67" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2385,10 +2384,10 @@
         <v>69</v>
       </c>
       <c r="D68" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E68" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2402,10 +2401,10 @@
         <v>70</v>
       </c>
       <c r="D69" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E69" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2419,10 +2418,10 @@
         <v>71</v>
       </c>
       <c r="D70" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E70" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2436,10 +2435,10 @@
         <v>71</v>
       </c>
       <c r="D71" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E71" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2453,10 +2452,10 @@
         <v>72</v>
       </c>
       <c r="D72" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E72" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2470,10 +2469,10 @@
         <v>73</v>
       </c>
       <c r="D73" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E73" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2487,7 +2486,7 @@
         <v>109</v>
       </c>
       <c r="D74" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E74" t="s">
         <v>16</v>
@@ -2504,7 +2503,7 @@
         <v>110</v>
       </c>
       <c r="D75" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E75" t="s">
         <v>16</v>
@@ -2521,7 +2520,7 @@
         <v>111</v>
       </c>
       <c r="D76" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
@@ -2538,7 +2537,7 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E77" t="s">
         <v>16</v>
@@ -2555,7 +2554,7 @@
         <v>113</v>
       </c>
       <c r="D78" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E78" t="s">
         <v>16</v>
@@ -2572,7 +2571,7 @@
         <v>114</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E79" t="s">
         <v>16</v>
@@ -2589,10 +2588,10 @@
         <v>74</v>
       </c>
       <c r="D80" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E80" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2606,10 +2605,10 @@
         <v>75</v>
       </c>
       <c r="D81" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E81" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2623,10 +2622,10 @@
         <v>76</v>
       </c>
       <c r="D82" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E82" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2640,10 +2639,10 @@
         <v>77</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E83" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2657,10 +2656,10 @@
         <v>177</v>
       </c>
       <c r="D84" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E84" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2674,10 +2673,10 @@
         <v>178</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E85" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2691,7 +2690,7 @@
         <v>179</v>
       </c>
       <c r="D86" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E86" t="s">
         <v>16</v>
@@ -2708,7 +2707,7 @@
         <v>180</v>
       </c>
       <c r="D87" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E87" t="s">
         <v>16</v>
@@ -2725,7 +2724,7 @@
         <v>181</v>
       </c>
       <c r="D88" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
@@ -2742,7 +2741,7 @@
         <v>182</v>
       </c>
       <c r="D89" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E89" t="s">
         <v>16</v>
@@ -2759,7 +2758,7 @@
         <v>183</v>
       </c>
       <c r="D90" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E90" t="s">
         <v>16</v>
@@ -2776,7 +2775,7 @@
         <v>184</v>
       </c>
       <c r="D91" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E91" t="s">
         <v>16</v>
@@ -2793,7 +2792,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
@@ -2810,7 +2809,7 @@
         <v>79</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E93" t="s">
         <v>16</v>
@@ -2827,7 +2826,7 @@
         <v>80</v>
       </c>
       <c r="D94" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E94" t="s">
         <v>16</v>
@@ -2844,7 +2843,7 @@
         <v>81</v>
       </c>
       <c r="D95" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
@@ -2861,7 +2860,7 @@
         <v>82</v>
       </c>
       <c r="D96" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E96" t="s">
         <v>16</v>
@@ -2878,7 +2877,7 @@
         <v>83</v>
       </c>
       <c r="D97" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E97" t="s">
         <v>16</v>
@@ -2895,10 +2894,10 @@
         <v>84</v>
       </c>
       <c r="D98" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E98" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -2912,10 +2911,10 @@
         <v>85</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E99" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -2929,10 +2928,10 @@
         <v>86</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E100" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2946,10 +2945,10 @@
         <v>87</v>
       </c>
       <c r="D101" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E101" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2963,10 +2962,10 @@
         <v>88</v>
       </c>
       <c r="D102" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E102" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2980,10 +2979,10 @@
         <v>89</v>
       </c>
       <c r="D103" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E103" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2997,7 +2996,7 @@
         <v>103</v>
       </c>
       <c r="D104" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E104" t="s">
         <v>16</v>
@@ -3014,7 +3013,7 @@
         <v>104</v>
       </c>
       <c r="D105" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E105" t="s">
         <v>16</v>
@@ -3031,7 +3030,7 @@
         <v>105</v>
       </c>
       <c r="D106" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E106" t="s">
         <v>16</v>
@@ -3048,7 +3047,7 @@
         <v>106</v>
       </c>
       <c r="D107" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E107" t="s">
         <v>16</v>
@@ -3065,7 +3064,7 @@
         <v>107</v>
       </c>
       <c r="D108" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
@@ -3082,7 +3081,7 @@
         <v>108</v>
       </c>
       <c r="D109" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E109" t="s">
         <v>16</v>
@@ -3096,13 +3095,13 @@
         <v>20</v>
       </c>
       <c r="C110" t="s">
-        <v>185</v>
+        <v>288</v>
       </c>
       <c r="D110" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E110" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -3113,13 +3112,13 @@
         <v>23</v>
       </c>
       <c r="C111" t="s">
-        <v>186</v>
+        <v>289</v>
       </c>
       <c r="D111" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E111" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -3130,13 +3129,13 @@
         <v>21</v>
       </c>
       <c r="C112" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D112" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E112" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3147,13 +3146,13 @@
         <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D113" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E113" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3164,13 +3163,13 @@
         <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D114" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E114" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3181,13 +3180,13 @@
         <v>25</v>
       </c>
       <c r="C115" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D115" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E115" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3201,7 +3200,7 @@
         <v>122</v>
       </c>
       <c r="D116" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E116" t="s">
         <v>16</v>
@@ -3218,7 +3217,7 @@
         <v>121</v>
       </c>
       <c r="D117" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E117" t="s">
         <v>16</v>
@@ -3235,7 +3234,7 @@
         <v>123</v>
       </c>
       <c r="D118" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E118" t="s">
         <v>16</v>
@@ -3252,7 +3251,7 @@
         <v>124</v>
       </c>
       <c r="D119" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
@@ -3269,7 +3268,7 @@
         <v>125</v>
       </c>
       <c r="D120" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E120" t="s">
         <v>16</v>
@@ -3286,7 +3285,7 @@
         <v>126</v>
       </c>
       <c r="D121" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E121" t="s">
         <v>16</v>
@@ -3303,10 +3302,10 @@
         <v>115</v>
       </c>
       <c r="D122" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E122" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3320,10 +3319,10 @@
         <v>116</v>
       </c>
       <c r="D123" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E123" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3337,10 +3336,10 @@
         <v>117</v>
       </c>
       <c r="D124" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E124" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3354,10 +3353,10 @@
         <v>118</v>
       </c>
       <c r="D125" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E125" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3371,10 +3370,10 @@
         <v>119</v>
       </c>
       <c r="D126" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E126" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3388,10 +3387,10 @@
         <v>120</v>
       </c>
       <c r="D127" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E127" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3405,7 +3404,7 @@
         <v>90</v>
       </c>
       <c r="D128" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E128" t="s">
         <v>16</v>
@@ -3422,7 +3421,7 @@
         <v>91</v>
       </c>
       <c r="D129" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
@@ -3439,7 +3438,7 @@
         <v>92</v>
       </c>
       <c r="D130" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
@@ -3456,7 +3455,7 @@
         <v>93</v>
       </c>
       <c r="D131" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E131" t="s">
         <v>16</v>
@@ -3470,10 +3469,10 @@
         <v>22</v>
       </c>
       <c r="C132" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D132" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E132" t="s">
         <v>16</v>
@@ -3487,10 +3486,10 @@
         <v>25</v>
       </c>
       <c r="C133" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D133" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E133" t="s">
         <v>16</v>
@@ -3507,10 +3506,10 @@
         <v>94</v>
       </c>
       <c r="D134" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E134" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3524,10 +3523,10 @@
         <v>95</v>
       </c>
       <c r="D135" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E135" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3541,10 +3540,10 @@
         <v>96</v>
       </c>
       <c r="D136" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E136" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -3558,10 +3557,10 @@
         <v>97</v>
       </c>
       <c r="D137" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E137" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -3575,10 +3574,10 @@
         <v>98</v>
       </c>
       <c r="D138" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E138" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -3592,10 +3591,10 @@
         <v>99</v>
       </c>
       <c r="D139" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E139" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -3609,7 +3608,7 @@
         <v>127</v>
       </c>
       <c r="D140" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E140" t="s">
         <v>16</v>
@@ -3626,7 +3625,7 @@
         <v>128</v>
       </c>
       <c r="D141" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E141" t="s">
         <v>16</v>
@@ -3643,7 +3642,7 @@
         <v>129</v>
       </c>
       <c r="D142" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E142" t="s">
         <v>16</v>
@@ -3660,7 +3659,7 @@
         <v>130</v>
       </c>
       <c r="D143" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E143" t="s">
         <v>16</v>
@@ -3677,7 +3676,7 @@
         <v>131</v>
       </c>
       <c r="D144" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E144" t="s">
         <v>16</v>
@@ -3694,7 +3693,7 @@
         <v>132</v>
       </c>
       <c r="D145" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E145" t="s">
         <v>16</v>
@@ -3736,7 +3735,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -3750,7 +3749,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -3764,7 +3763,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -3778,7 +3777,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -3792,7 +3791,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -3806,7 +3805,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -3820,7 +3819,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -3834,7 +3833,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -3845,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
@@ -3859,10 +3858,10 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
@@ -3873,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -3887,10 +3886,10 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -3901,13 +3900,13 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -3915,13 +3914,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -3929,13 +3928,13 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -3943,13 +3942,13 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -3957,13 +3956,13 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -3971,13 +3970,13 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -3985,13 +3984,13 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -3999,13 +3998,13 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4016,10 +4015,10 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4030,10 +4029,10 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -4044,10 +4043,10 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -4058,10 +4057,10 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -4091,142 +4090,142 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -4234,10 +4233,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -4245,10 +4244,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B16" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -4256,10 +4255,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -4267,10 +4266,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C18" t="s">
         <v>16</v>
@@ -4278,10 +4277,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
@@ -4289,10 +4288,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
@@ -4300,10 +4299,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
@@ -4311,10 +4310,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B22" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C22" t="s">
         <v>16</v>
@@ -4322,10 +4321,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -4333,10 +4332,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -4344,10 +4343,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
